--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abbott India Ltd</t>
+          <t>ABB India Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,12 +476,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABB India Ltd</t>
+          <t>Abbott India Ltd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -500,7 +500,7 @@
         <v>62.63</v>
       </c>
       <c r="I2" t="n">
-        <v>60.27992789735976</v>
+        <v>58.38222967309304</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         <v>58.87</v>
       </c>
       <c r="I4" t="n">
-        <v>24.84360089067966</v>
+        <v>29.64104822726272</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         <v>48.9</v>
       </c>
       <c r="I6" t="n">
-        <v>3.700561976460603</v>
+        <v>7.685531821184766</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>28.39</v>
       </c>
       <c r="I9" t="n">
-        <v>1.402464938376533</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>52.67</v>
       </c>
       <c r="I18" t="n">
-        <v>-62.06128724419467</v>
+        <v>-60.60339132349702</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>31.13</v>
       </c>
       <c r="I20" t="n">
-        <v>-36.80415650514261</v>
+        <v>-34.37568817441092</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>41.07</v>
       </c>
       <c r="I26" t="n">
-        <v>26.96557586060348</v>
+        <v>25.20955574182733</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>30.35</v>
       </c>
       <c r="I29" t="n">
-        <v>48.64003399915002</v>
+        <v>46.5842414082146</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>13.03</v>
       </c>
       <c r="I32" t="n">
-        <v>-75.07437314067148</v>
+        <v>-75.41911148365465</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>38.27</v>
       </c>
       <c r="I36" t="n">
-        <v>68.27483829922593</v>
+        <v>74.74124642149307</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>51.22</v>
       </c>
       <c r="I37" t="n">
-        <v>52.45467076662072</v>
+        <v>58.31314688394627</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45.41</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.700561976460618</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>18.77</v>
       </c>
       <c r="I62" t="n">
-        <v>-34.68349061605344</v>
+        <v>-32.17353005945826</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>41.13</v>
       </c>
       <c r="I82" t="n">
-        <v>-29.33941257554872</v>
+        <v>-26.62409160977758</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>24.58</v>
       </c>
       <c r="I83" t="n">
-        <v>-19.46451338716533</v>
+        <v>-20.57837384744342</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>46.4</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.402464938376548</v>
+        <v>-2.766135792120705</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>

--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -434,22 +434,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>pe_ratio</t>
+          <t>P/E</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>pb_ratio</t>
+          <t>P/B</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ev_ebitda</t>
+          <t>EV/EBITDA</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>fcf_yield_pct</t>
+          <t>FCF_yield_pct</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -494,13 +494,13 @@
         <v>12.63</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05188004157485571</v>
+        <v>0.07127809977975783</v>
       </c>
       <c r="H2" t="n">
-        <v>62.63</v>
+        <v>60.485</v>
       </c>
       <c r="I2" t="n">
-        <v>58.38222967309304</v>
+        <v>60.27992789735976</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         <v>0.3141880794689826</v>
       </c>
       <c r="H3" t="n">
-        <v>58.5</v>
+        <v>59.075</v>
       </c>
       <c r="I3" t="n">
         <v>30.24602026049204</v>
@@ -577,10 +577,10 @@
         <v>-4.499064189327432</v>
       </c>
       <c r="H4" t="n">
-        <v>58.87</v>
+        <v>57.5</v>
       </c>
       <c r="I4" t="n">
-        <v>29.64104822726272</v>
+        <v>24.84360089067966</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         <v>-2.61443014217979</v>
       </c>
       <c r="H5" t="n">
-        <v>37.61</v>
+        <v>33.34</v>
       </c>
       <c r="I5" t="n">
         <v>0.7681175553823865</v>
@@ -658,10 +658,10 @@
         <v>1.221140364223394</v>
       </c>
       <c r="H6" t="n">
-        <v>48.9</v>
+        <v>49.83</v>
       </c>
       <c r="I6" t="n">
-        <v>7.685531821184766</v>
+        <v>3.700561976460603</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>1.286343944292292</v>
       </c>
       <c r="H7" t="n">
-        <v>52.23</v>
+        <v>48.4</v>
       </c>
       <c r="I7" t="n">
         <v>-0.7681175553823865</v>
@@ -738,7 +738,7 @@
         <v>-0.2571384120430241</v>
       </c>
       <c r="H8" t="n">
-        <v>55.62</v>
+        <v>50.985</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -779,10 +779,10 @@
         <v>0.0200984200212211</v>
       </c>
       <c r="H9" t="n">
-        <v>28.39</v>
+        <v>38.055</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1.402464938376533</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>0.167205430839917</v>
       </c>
       <c r="H10" t="n">
-        <v>49.2</v>
+        <v>44.905</v>
       </c>
       <c r="I10" t="n">
         <v>31.91298094210717</v>
@@ -856,11 +856,9 @@
       <c r="F11" t="n">
         <v>28.93</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>35.59</v>
+        <v>31.8</v>
       </c>
       <c r="I11" t="n">
         <v>26.8173216074808</v>
@@ -900,7 +898,7 @@
         <v>-1.534037435719632</v>
       </c>
       <c r="H12" t="n">
-        <v>56.88</v>
+        <v>47.88</v>
       </c>
       <c r="I12" t="n">
         <v>11.39018691588785</v>
@@ -940,7 +938,7 @@
         <v>0.992020247858232</v>
       </c>
       <c r="H13" t="n">
-        <v>49.72</v>
+        <v>49.565</v>
       </c>
       <c r="I13" t="n">
         <v>-21.29982896987239</v>
@@ -980,7 +978,7 @@
         <v>-4.180016339930263</v>
       </c>
       <c r="H14" t="n">
-        <v>51.06</v>
+        <v>47.335</v>
       </c>
       <c r="I14" t="n">
         <v>-55.98714953271028</v>
@@ -1020,7 +1018,7 @@
         <v>0.06702962960133939</v>
       </c>
       <c r="H15" t="n">
-        <v>37.73</v>
+        <v>44.245</v>
       </c>
       <c r="I15" t="n">
         <v>10.19275700934578</v>
@@ -1060,7 +1058,7 @@
         <v>-3.231792280571145</v>
       </c>
       <c r="H16" t="n">
-        <v>46.9</v>
+        <v>50.87</v>
       </c>
       <c r="I16" t="n">
         <v>102.1028037383177</v>
@@ -1100,7 +1098,7 @@
         <v>-1.279081332956056</v>
       </c>
       <c r="H17" t="n">
-        <v>67.23999999999999</v>
+        <v>51.62</v>
       </c>
       <c r="I17" t="n">
         <v>-50.67172897196262</v>
@@ -1140,10 +1138,10 @@
         <v>-0.09337302073000636</v>
       </c>
       <c r="H18" t="n">
-        <v>52.67</v>
+        <v>56.305</v>
       </c>
       <c r="I18" t="n">
-        <v>-60.60339132349702</v>
+        <v>-62.06128724419467</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1180,7 +1178,7 @@
         <v>7.345106122639473</v>
       </c>
       <c r="H19" t="n">
-        <v>63.78</v>
+        <v>65.33500000000001</v>
       </c>
       <c r="I19" t="n">
         <v>31.967721911856</v>
@@ -1221,10 +1219,10 @@
         <v>-0.4410671269170658</v>
       </c>
       <c r="H20" t="n">
-        <v>31.13</v>
+        <v>35.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-34.37568817441092</v>
+        <v>-36.80415650514261</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1261,7 +1259,7 @@
         <v>0.05908701218425355</v>
       </c>
       <c r="H21" t="n">
-        <v>31.28</v>
+        <v>34.555</v>
       </c>
       <c r="I21" t="n">
         <v>53.7429285620313</v>
@@ -1301,7 +1299,7 @@
         <v>5.422883218663305</v>
       </c>
       <c r="H22" t="n">
-        <v>35.8</v>
+        <v>30.585</v>
       </c>
       <c r="I22" t="n">
         <v>51.73104753423134</v>
@@ -1341,7 +1339,7 @@
         <v>0.9391963078561093</v>
       </c>
       <c r="H23" t="n">
-        <v>33.6</v>
+        <v>36.77500000000001</v>
       </c>
       <c r="I23" t="n">
         <v>25.43670264965651</v>
@@ -1381,7 +1379,7 @@
         <v>2.678399409785198</v>
       </c>
       <c r="H24" t="n">
-        <v>36.74</v>
+        <v>34.745</v>
       </c>
       <c r="I24" t="n">
         <v>7.301401869158878</v>
@@ -1421,7 +1419,7 @@
         <v>-3.965092371280805</v>
       </c>
       <c r="H25" t="n">
-        <v>33.3</v>
+        <v>28.41</v>
       </c>
       <c r="I25" t="n">
         <v>-50.96378504672898</v>
@@ -1462,10 +1460,10 @@
         <v>0.2619353681300373</v>
       </c>
       <c r="H26" t="n">
-        <v>41.07</v>
+        <v>50.41</v>
       </c>
       <c r="I26" t="n">
-        <v>25.20955574182733</v>
+        <v>26.96557586060348</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1502,7 +1500,7 @@
         <v>2.999175111211977</v>
       </c>
       <c r="H27" t="n">
-        <v>32.17</v>
+        <v>33.22</v>
       </c>
       <c r="I27" t="n">
         <v>-38.38547285149226</v>
@@ -1542,7 +1540,7 @@
         <v>1.843535171537232</v>
       </c>
       <c r="H28" t="n">
-        <v>50.95</v>
+        <v>41.055</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1582,10 +1580,10 @@
         <v>0.0614230582049048</v>
       </c>
       <c r="H29" t="n">
-        <v>30.35</v>
+        <v>43.625</v>
       </c>
       <c r="I29" t="n">
-        <v>46.5842414082146</v>
+        <v>48.64003399915002</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1622,7 +1620,7 @@
         <v>0.07309772065891328</v>
       </c>
       <c r="H30" t="n">
-        <v>46.26</v>
+        <v>42.20999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>-5.793707361775798</v>
@@ -1662,7 +1660,7 @@
         <v>0.00910553222430331</v>
       </c>
       <c r="H31" t="n">
-        <v>37.82</v>
+        <v>45.655</v>
       </c>
       <c r="I31" t="n">
         <v>90.84331009077752</v>
@@ -1702,10 +1700,10 @@
         <v>0.02084525007272494</v>
       </c>
       <c r="H32" t="n">
-        <v>13.03</v>
+        <v>12.38</v>
       </c>
       <c r="I32" t="n">
-        <v>-75.41911148365465</v>
+        <v>-75.07437314067148</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1742,7 +1740,7 @@
         <v>0.4001945575069012</v>
       </c>
       <c r="H33" t="n">
-        <v>18.91</v>
+        <v>21.865</v>
       </c>
       <c r="I33" t="n">
         <v>-58.90014471780029</v>
@@ -1782,7 +1780,7 @@
         <v>0.2846199035338283</v>
       </c>
       <c r="H34" t="n">
-        <v>30.66</v>
+        <v>28.26</v>
       </c>
       <c r="I34" t="n">
         <v>-42.46910831570745</v>
@@ -1822,7 +1820,7 @@
         <v>-0.1028018435345398</v>
       </c>
       <c r="H35" t="n">
-        <v>40.79</v>
+        <v>37.19</v>
       </c>
       <c r="I35" t="n">
         <v>-34.07262021589793</v>
@@ -1862,10 +1860,10 @@
         <v>-7.063967310949983</v>
       </c>
       <c r="H36" t="n">
-        <v>38.27</v>
+        <v>47.49</v>
       </c>
       <c r="I36" t="n">
-        <v>74.74124642149307</v>
+        <v>68.27483829922593</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1902,10 +1900,10 @@
         <v>0.06861811283803056</v>
       </c>
       <c r="H37" t="n">
-        <v>51.22</v>
+        <v>53.635</v>
       </c>
       <c r="I37" t="n">
-        <v>58.31314688394627</v>
+        <v>52.45467076662072</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1942,10 +1940,10 @@
         <v>0.01328569587780193</v>
       </c>
       <c r="H38" t="n">
-        <v>45.41</v>
+        <v>55.345</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>-3.700561976460618</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1982,7 +1980,7 @@
         <v>3.839131751270119</v>
       </c>
       <c r="H39" t="n">
-        <v>63.63</v>
+        <v>62.05</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2022,7 +2020,7 @@
         <v>4.412519521183551</v>
       </c>
       <c r="H40" t="n">
-        <v>30.19</v>
+        <v>31.84</v>
       </c>
       <c r="I40" t="n">
         <v>44.33411214953271</v>
@@ -2062,7 +2060,7 @@
         <v>-6.151706657367163</v>
       </c>
       <c r="H41" t="n">
-        <v>50.59</v>
+        <v>52.28</v>
       </c>
       <c r="I41" t="n">
         <v>47.75116822429906</v>
@@ -2103,7 +2101,7 @@
         <v>0.1942386275072222</v>
       </c>
       <c r="H42" t="n">
-        <v>56.18</v>
+        <v>60.27500000000001</v>
       </c>
       <c r="I42" t="n">
         <v>41.71819497434547</v>
@@ -2143,7 +2141,7 @@
         <v>1.355289512628809</v>
       </c>
       <c r="H43" t="n">
-        <v>56.45</v>
+        <v>51.02</v>
       </c>
       <c r="I43" t="n">
         <v>1.492268967997133</v>
@@ -2184,7 +2182,7 @@
         <v>1.848273624075064</v>
       </c>
       <c r="H44" t="n">
-        <v>22.92</v>
+        <v>21.805</v>
       </c>
       <c r="I44" t="n">
         <v>-32.26692836113838</v>
@@ -2224,7 +2222,7 @@
         <v>0.9510909711578005</v>
       </c>
       <c r="H45" t="n">
-        <v>25.76</v>
+        <v>50.57</v>
       </c>
       <c r="I45" t="n">
         <v>-24.76635514018692</v>
@@ -2264,7 +2262,7 @@
         <v>0.03821387979852416</v>
       </c>
       <c r="H46" t="n">
-        <v>49</v>
+        <v>52.4</v>
       </c>
       <c r="I46" t="n">
         <v>43.10747663551401</v>
@@ -2304,7 +2302,7 @@
         <v>0.006574879059013327</v>
       </c>
       <c r="H47" t="n">
-        <v>36.03</v>
+        <v>44.31</v>
       </c>
       <c r="I47" t="n">
         <v>-39.16471962616824</v>
@@ -2344,7 +2342,7 @@
         <v>0.9056027172386589</v>
       </c>
       <c r="H48" t="n">
-        <v>51.42</v>
+        <v>53.7</v>
       </c>
       <c r="I48" t="n">
         <v>100.5788712011577</v>
@@ -2384,7 +2382,7 @@
         <v>-0.9664534641259643</v>
       </c>
       <c r="H49" t="n">
-        <v>51.73</v>
+        <v>56</v>
       </c>
       <c r="I49" t="n">
         <v>-73.74415887850468</v>
@@ -2424,7 +2422,7 @@
         <v>1.808627454139422</v>
       </c>
       <c r="H50" t="n">
-        <v>35.99</v>
+        <v>34.31</v>
       </c>
       <c r="I50" t="n">
         <v>-43.43862957724344</v>
@@ -2465,7 +2463,7 @@
         <v>2.794810104975634</v>
       </c>
       <c r="H51" t="n">
-        <v>50.51</v>
+        <v>49.11</v>
       </c>
       <c r="I51" t="n">
         <v>-36.30190359568073</v>
@@ -2505,7 +2503,7 @@
         <v>0.05299874823631171</v>
       </c>
       <c r="H52" t="n">
-        <v>36.42</v>
+        <v>45.585</v>
       </c>
       <c r="I52" t="n">
         <v>59.03170635442703</v>
@@ -2545,7 +2543,7 @@
         <v>0.3019460457018293</v>
       </c>
       <c r="H53" t="n">
-        <v>37.81</v>
+        <v>36.52</v>
       </c>
       <c r="I53" t="n">
         <v>-71.34929906542055</v>
@@ -2586,7 +2584,7 @@
         <v>5.641008076014133</v>
       </c>
       <c r="H54" t="n">
-        <v>55.53</v>
+        <v>62.555</v>
       </c>
       <c r="I54" t="n">
         <v>-6.084396467124634</v>
@@ -2626,7 +2624,7 @@
         <v>-0.5890244225007633</v>
       </c>
       <c r="H55" t="n">
-        <v>47.36</v>
+        <v>43.26</v>
       </c>
       <c r="I55" t="n">
         <v>39.59007551240561</v>
@@ -2666,7 +2664,7 @@
         <v>0.05443098966974722</v>
       </c>
       <c r="H56" t="n">
-        <v>65.98</v>
+        <v>50.11</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -2706,7 +2704,7 @@
         <v>-1.77053361249378</v>
       </c>
       <c r="H57" t="n">
-        <v>36.57</v>
+        <v>37.545</v>
       </c>
       <c r="I57" t="n">
         <v>-44.80685739730602</v>
@@ -2746,7 +2744,7 @@
         <v>-0.09143985264473488</v>
       </c>
       <c r="H58" t="n">
-        <v>36.76</v>
+        <v>35.885</v>
       </c>
       <c r="I58" t="n">
         <v>24.54153182308522</v>
@@ -2787,7 +2785,7 @@
         <v>1.572670875827523</v>
       </c>
       <c r="H59" t="n">
-        <v>43.71</v>
+        <v>46.535</v>
       </c>
       <c r="I59" t="n">
         <v>-3.913551401869168</v>
@@ -2827,7 +2825,7 @@
         <v>0.4646382763782856</v>
       </c>
       <c r="H60" t="n">
-        <v>30.67</v>
+        <v>34.485</v>
       </c>
       <c r="I60" t="n">
         <v>-10.42640186915888</v>
@@ -2867,7 +2865,7 @@
         <v>-0.03595279056427525</v>
       </c>
       <c r="H61" t="n">
-        <v>51.95</v>
+        <v>52.13</v>
       </c>
       <c r="I61" t="n">
         <v>5.793707361775784</v>
@@ -2907,10 +2905,10 @@
         <v>1.817983767525715</v>
       </c>
       <c r="H62" t="n">
-        <v>18.77</v>
+        <v>24.09</v>
       </c>
       <c r="I62" t="n">
-        <v>-32.17353005945826</v>
+        <v>-34.68349061605344</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2947,7 +2945,7 @@
         <v>0.1300622866212008</v>
       </c>
       <c r="H63" t="n">
-        <v>61.37</v>
+        <v>60.765</v>
       </c>
       <c r="I63" t="n">
         <v>1.398711299701388</v>
@@ -2988,7 +2986,7 @@
         <v>-0.2694648852484086</v>
       </c>
       <c r="H64" t="n">
-        <v>34.84</v>
+        <v>43.58</v>
       </c>
       <c r="I64" t="n">
         <v>-62.58387054334956</v>
@@ -3028,7 +3026,7 @@
         <v>0.3282212496887102</v>
       </c>
       <c r="H65" t="n">
-        <v>20.78</v>
+        <v>28.565</v>
       </c>
       <c r="I65" t="n">
         <v>-45.3229838179187</v>
@@ -3068,7 +3066,7 @@
         <v>0.6329063689949501</v>
       </c>
       <c r="H66" t="n">
-        <v>30.92</v>
+        <v>31.5</v>
       </c>
       <c r="I66" t="n">
         <v>-74.89803973161426</v>
@@ -3108,7 +3106,7 @@
         <v>-0.02660402589146366</v>
       </c>
       <c r="H67" t="n">
-        <v>36.89</v>
+        <v>34.88500000000001</v>
       </c>
       <c r="I67" t="n">
         <v>-31.96772191185599</v>
@@ -3148,7 +3146,7 @@
         <v>0.175112852872738</v>
       </c>
       <c r="H68" t="n">
-        <v>46.21</v>
+        <v>50.585</v>
       </c>
       <c r="I68" t="n">
         <v>7.870461236506375</v>
@@ -3189,7 +3187,7 @@
         <v>0.05573417784977254</v>
       </c>
       <c r="H69" t="n">
-        <v>59.63</v>
+        <v>59.83</v>
       </c>
       <c r="I69" t="n">
         <v>58.45485917844818</v>
@@ -3229,7 +3227,7 @@
         <v>0.9521678733206076</v>
       </c>
       <c r="H70" t="n">
-        <v>54.44</v>
+        <v>44.12</v>
       </c>
       <c r="I70" t="n">
         <v>-31.42602693977513</v>
@@ -3269,7 +3267,7 @@
         <v>10.78154540867274</v>
       </c>
       <c r="H71" t="n">
-        <v>43.8</v>
+        <v>44.31</v>
       </c>
       <c r="I71" t="n">
         <v>-59.59033730379606</v>
@@ -3309,7 +3307,7 @@
         <v>-5.031547988302576</v>
       </c>
       <c r="H72" t="n">
-        <v>35.6</v>
+        <v>35.95</v>
       </c>
       <c r="I72" t="n">
         <v>3.971962616822428</v>
@@ -3349,7 +3347,7 @@
         <v>0.588510137595519</v>
       </c>
       <c r="H73" t="n">
-        <v>38.11</v>
+        <v>37.11499999999999</v>
       </c>
       <c r="I73" t="n">
         <v>-35.05933117583604</v>
@@ -3389,7 +3387,7 @@
         <v>-1.612606778720886</v>
       </c>
       <c r="H74" t="n">
-        <v>20.42</v>
+        <v>20.58</v>
       </c>
       <c r="I74" t="n">
         <v>-43.6623831775701</v>
@@ -3429,7 +3427,7 @@
         <v>6.488733930345523</v>
       </c>
       <c r="H75" t="n">
-        <v>37.33</v>
+        <v>50.86</v>
       </c>
       <c r="I75" t="n">
         <v>43.35967939441167</v>
@@ -3469,7 +3467,7 @@
         <v>-20.40097504287343</v>
       </c>
       <c r="H76" t="n">
-        <v>31.49</v>
+        <v>43.34</v>
       </c>
       <c r="I76" t="n">
         <v>-8.031542056074777</v>
@@ -3510,7 +3508,7 @@
         <v>10.45314512446346</v>
       </c>
       <c r="H77" t="n">
-        <v>58.34</v>
+        <v>50.5</v>
       </c>
       <c r="I77" t="n">
         <v>29.88979182901036</v>
@@ -3550,7 +3548,7 @@
         <v>-0.2368813254240325</v>
       </c>
       <c r="H78" t="n">
-        <v>60.68</v>
+        <v>54.025</v>
       </c>
       <c r="I78" t="n">
         <v>104.3808411214953</v>
@@ -3590,7 +3588,7 @@
         <v>0.7563625783740417</v>
       </c>
       <c r="H79" t="n">
-        <v>54.93</v>
+        <v>50.985</v>
       </c>
       <c r="I79" t="n">
         <v>60.42640186915887</v>
@@ -3630,7 +3628,7 @@
         <v>0.06115348347250073</v>
       </c>
       <c r="H80" t="n">
-        <v>32.7</v>
+        <v>33.97</v>
       </c>
       <c r="I80" t="n">
         <v>-53.48795397339087</v>
@@ -3671,7 +3669,7 @@
         <v>-3.608906905151208</v>
       </c>
       <c r="H81" t="n">
-        <v>37.85</v>
+        <v>47.26000000000001</v>
       </c>
       <c r="I81" t="n">
         <v>100.1460280373832</v>
@@ -3707,12 +3705,14 @@
       <c r="F82" t="n">
         <v>30.88</v>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>0.09804152402695152</v>
+      </c>
       <c r="H82" t="n">
-        <v>41.13</v>
+        <v>37.225</v>
       </c>
       <c r="I82" t="n">
-        <v>-26.62409160977758</v>
+        <v>-29.33941257554872</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3749,10 +3749,10 @@
         <v>0.8489189373413096</v>
       </c>
       <c r="H83" t="n">
-        <v>24.58</v>
+        <v>31.24</v>
       </c>
       <c r="I83" t="n">
-        <v>-20.57837384744342</v>
+        <v>-19.46451338716533</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>0.007417056977403794</v>
       </c>
       <c r="H84" t="n">
-        <v>54.79</v>
+        <v>37.655</v>
       </c>
       <c r="I84" t="n">
         <v>7.536800785083407</v>
@@ -3829,7 +3829,7 @@
         <v>3.000651602734764</v>
       </c>
       <c r="H85" t="n">
-        <v>34.17</v>
+        <v>31.715</v>
       </c>
       <c r="I85" t="n">
         <v>76.47677937113535</v>
@@ -3870,7 +3870,7 @@
         <v>0.2166615750083587</v>
       </c>
       <c r="H86" t="n">
-        <v>24.7</v>
+        <v>23.51</v>
       </c>
       <c r="I86" t="n">
         <v>-67.71679839697205</v>
@@ -3911,7 +3911,7 @@
         <v>1.638533052351645</v>
       </c>
       <c r="H87" t="n">
-        <v>48.97</v>
+        <v>50.555</v>
       </c>
       <c r="I87" t="n">
         <v>-11.95613088816972</v>
@@ -3951,7 +3951,7 @@
         <v>10.93458277277939</v>
       </c>
       <c r="H88" t="n">
-        <v>57.2</v>
+        <v>52.365</v>
       </c>
       <c r="I88" t="n">
         <v>23.66808109382366</v>
@@ -3991,7 +3991,7 @@
         <v>0.1674227036387368</v>
       </c>
       <c r="H89" t="n">
-        <v>51.58</v>
+        <v>49.445</v>
       </c>
       <c r="I89" t="n">
         <v>-9.790979097909796</v>
@@ -4032,7 +4032,7 @@
         <v>0.0839572651499547</v>
       </c>
       <c r="H90" t="n">
-        <v>26.55</v>
+        <v>27.58</v>
       </c>
       <c r="I90" t="n">
         <v>-73.34561241941849</v>
@@ -4072,10 +4072,10 @@
         <v>0.1660811237632738</v>
       </c>
       <c r="H91" t="n">
-        <v>46.4</v>
+        <v>48.83</v>
       </c>
       <c r="I91" t="n">
-        <v>-2.766135792120705</v>
+        <v>-1.402464938376548</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>0.1472024429514394</v>
       </c>
       <c r="H92" t="n">
-        <v>65.94</v>
+        <v>67.02</v>
       </c>
       <c r="I92" t="n">
         <v>-77.23983686357059</v>
@@ -4152,7 +4152,7 @@
         <v>-0.8454886074536311</v>
       </c>
       <c r="H93" t="n">
-        <v>46.1</v>
+        <v>35.19</v>
       </c>
       <c r="I93" t="n">
         <v>21.29982896987238</v>

--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,27 +429,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>sector</t>
+          <t>broad_sector</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>P/E</t>
+          <t>pe_ratio</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>P/B</t>
+          <t>pb_ratio</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>EV/EBITDA</t>
+          <t>ev_ebitda</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>FCF_yield_pct</t>
+          <t>fcf_yield_pct</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -459,12 +459,17 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>PE_vs_sector_median_pct</t>
+          <t>pe_vs_sector_median_pct</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>flag</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>5yr_median_PE_actual</t>
         </is>
       </c>
     </row>
@@ -497,7 +502,7 @@
         <v>0.07127809977975783</v>
       </c>
       <c r="H2" t="n">
-        <v>60.485</v>
+        <v>47.155</v>
       </c>
       <c r="I2" t="n">
         <v>60.27992789735976</v>
@@ -507,6 +512,9 @@
           <t>Caution</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>60.485</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -537,15 +545,18 @@
         <v>0.3141880794689826</v>
       </c>
       <c r="H3" t="n">
+        <v>44.915</v>
+      </c>
+      <c r="I3" t="n">
+        <v>30.24602026049203</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>59.075</v>
-      </c>
-      <c r="I3" t="n">
-        <v>30.24602026049204</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -577,15 +588,18 @@
         <v>-4.499064189327432</v>
       </c>
       <c r="H4" t="n">
+        <v>47.155</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24.84360089067967</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>57.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>24.84360089067966</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -617,15 +631,18 @@
         <v>-2.61443014217979</v>
       </c>
       <c r="H5" t="n">
+        <v>44.915</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7681175553823971</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>33.34</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7681175553823865</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -636,8 +653,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adani Ports &amp; Special Economic Zone Ltd
-</t>
+          <t>Adani Ports &amp; Special Economic Zone Ltd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -658,7 +674,7 @@
         <v>1.221140364223394</v>
       </c>
       <c r="H6" t="n">
-        <v>49.83</v>
+        <v>47.155</v>
       </c>
       <c r="I6" t="n">
         <v>3.700561976460603</v>
@@ -668,6 +684,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>49.83</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -698,15 +717,18 @@
         <v>1.286343944292292</v>
       </c>
       <c r="H7" t="n">
+        <v>44.915</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.768117555382386</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>48.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.7681175553823865</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -738,7 +760,7 @@
         <v>-0.2571384120430241</v>
       </c>
       <c r="H8" t="n">
-        <v>50.985</v>
+        <v>55.62</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -748,6 +770,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>50.985</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -757,8 +782,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Apollo Hospitals
-Chain of Indian private hospitals</t>
+          <t>Apollo Hospitals Chain of Indian private hospitals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -779,15 +803,18 @@
         <v>0.0200984200212211</v>
       </c>
       <c r="H9" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.402464938376524</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>38.055</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.402464938376533</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -798,8 +825,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Asian Paints
-Indian Multi-National Paint and Coating Manufacturing Company</t>
+          <t>Asian Paints Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -820,7 +846,7 @@
         <v>0.167205430839917</v>
       </c>
       <c r="H10" t="n">
-        <v>44.905</v>
+        <v>55.62</v>
       </c>
       <c r="I10" t="n">
         <v>31.91298094210717</v>
@@ -830,6 +856,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>44.905</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -858,7 +887,7 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>31.8</v>
+        <v>44.915</v>
       </c>
       <c r="I11" t="n">
         <v>26.8173216074808</v>
@@ -868,6 +897,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>31.8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -898,7 +930,7 @@
         <v>-1.534037435719632</v>
       </c>
       <c r="H12" t="n">
-        <v>47.88</v>
+        <v>34.24</v>
       </c>
       <c r="I12" t="n">
         <v>11.39018691588785</v>
@@ -908,6 +940,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>47.88</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -938,7 +973,7 @@
         <v>0.992020247858232</v>
       </c>
       <c r="H13" t="n">
-        <v>49.565</v>
+        <v>38.005</v>
       </c>
       <c r="I13" t="n">
         <v>-21.29982896987239</v>
@@ -948,6 +983,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>49.565</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -978,15 +1016,18 @@
         <v>-4.180016339930263</v>
       </c>
       <c r="H14" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-55.98714953271029</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>47.335</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-55.98714953271028</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -1018,15 +1059,18 @@
         <v>0.06702962960133939</v>
       </c>
       <c r="H15" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.19275700934579</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>44.245</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10.19275700934578</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -1058,15 +1102,18 @@
         <v>-3.231792280571145</v>
       </c>
       <c r="H16" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I16" t="n">
+        <v>102.1028037383178</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>50.87</v>
-      </c>
-      <c r="I16" t="n">
-        <v>102.1028037383177</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -1098,7 +1145,7 @@
         <v>-1.279081332956056</v>
       </c>
       <c r="H17" t="n">
-        <v>51.62</v>
+        <v>34.24</v>
       </c>
       <c r="I17" t="n">
         <v>-50.67172897196262</v>
@@ -1108,6 +1155,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>51.62</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1138,15 +1188,18 @@
         <v>-0.09337302073000636</v>
       </c>
       <c r="H18" t="n">
+        <v>47.155</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-62.06128724419469</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>56.305</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-62.06128724419467</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -1178,7 +1231,7 @@
         <v>7.345106122639473</v>
       </c>
       <c r="H19" t="n">
-        <v>65.33500000000001</v>
+        <v>48.33</v>
       </c>
       <c r="I19" t="n">
         <v>31.967721911856</v>
@@ -1188,6 +1241,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>65.33500000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1197,8 +1253,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bharat Heavy Electricals Limited
-</t>
+          <t>Bharat Heavy Electricals Limited</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1219,7 +1274,7 @@
         <v>-0.4410671269170658</v>
       </c>
       <c r="H20" t="n">
-        <v>35.98</v>
+        <v>47.155</v>
       </c>
       <c r="I20" t="n">
         <v>-36.80415650514261</v>
@@ -1229,6 +1284,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>35.98</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1259,15 +1317,18 @@
         <v>0.05908701218425355</v>
       </c>
       <c r="H21" t="n">
+        <v>38.005</v>
+      </c>
+      <c r="I21" t="n">
+        <v>53.74292856203131</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>34.555</v>
-      </c>
-      <c r="I21" t="n">
-        <v>53.7429285620313</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -1299,7 +1360,7 @@
         <v>5.422883218663305</v>
       </c>
       <c r="H22" t="n">
-        <v>30.585</v>
+        <v>44.915</v>
       </c>
       <c r="I22" t="n">
         <v>51.73104753423134</v>
@@ -1309,6 +1370,9 @@
           <t>Caution</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>30.585</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1339,15 +1403,18 @@
         <v>0.9391963078561093</v>
       </c>
       <c r="H23" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="I23" t="n">
+        <v>25.43670264965652</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>36.77500000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>25.43670264965651</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -1379,15 +1446,18 @@
         <v>2.678399409785198</v>
       </c>
       <c r="H24" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.301401869158886</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>34.745</v>
-      </c>
-      <c r="I24" t="n">
-        <v>7.301401869158878</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -1419,7 +1489,7 @@
         <v>-3.965092371280805</v>
       </c>
       <c r="H25" t="n">
-        <v>28.41</v>
+        <v>34.24</v>
       </c>
       <c r="I25" t="n">
         <v>-50.96378504672898</v>
@@ -1429,6 +1499,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K25" t="n">
+        <v>28.41</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1438,8 +1511,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cipla Ltd
-</t>
+          <t>Cipla Ltd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1460,15 +1532,18 @@
         <v>0.2619353681300373</v>
       </c>
       <c r="H26" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="I26" t="n">
+        <v>26.96557586060349</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>50.41</v>
-      </c>
-      <c r="I26" t="n">
-        <v>26.96557586060348</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="27">
@@ -1500,15 +1575,18 @@
         <v>2.999175111211977</v>
       </c>
       <c r="H27" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-38.38547285149227</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>33.22</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-38.38547285149226</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -1540,7 +1618,7 @@
         <v>1.843535171537232</v>
       </c>
       <c r="H28" t="n">
-        <v>41.055</v>
+        <v>50.95</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1550,6 +1628,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>41.055</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1580,7 +1661,7 @@
         <v>0.0614230582049048</v>
       </c>
       <c r="H29" t="n">
-        <v>43.625</v>
+        <v>47.06</v>
       </c>
       <c r="I29" t="n">
         <v>48.64003399915002</v>
@@ -1590,6 +1671,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K29" t="n">
+        <v>43.625</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1620,15 +1704,18 @@
         <v>0.07309772065891328</v>
       </c>
       <c r="H30" t="n">
+        <v>49.105</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-5.793707361775802</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>42.20999999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-5.793707361775798</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="31">
@@ -1660,15 +1747,18 @@
         <v>0.00910553222430331</v>
       </c>
       <c r="H31" t="n">
+        <v>38.005</v>
+      </c>
+      <c r="I31" t="n">
+        <v>90.84331009077754</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>45.655</v>
-      </c>
-      <c r="I31" t="n">
-        <v>90.84331009077752</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
       </c>
     </row>
     <row r="32">
@@ -1700,7 +1790,7 @@
         <v>0.02084525007272494</v>
       </c>
       <c r="H32" t="n">
-        <v>12.38</v>
+        <v>47.06</v>
       </c>
       <c r="I32" t="n">
         <v>-75.07437314067148</v>
@@ -1710,6 +1800,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K32" t="n">
+        <v>12.38</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1740,7 +1833,7 @@
         <v>0.4001945575069012</v>
       </c>
       <c r="H33" t="n">
-        <v>21.865</v>
+        <v>38.005</v>
       </c>
       <c r="I33" t="n">
         <v>-58.90014471780029</v>
@@ -1750,6 +1843,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K33" t="n">
+        <v>21.865</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1780,7 +1876,7 @@
         <v>0.2846199035338283</v>
       </c>
       <c r="H34" t="n">
-        <v>28.26</v>
+        <v>44.915</v>
       </c>
       <c r="I34" t="n">
         <v>-42.46910831570745</v>
@@ -1790,6 +1886,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K34" t="n">
+        <v>28.26</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1820,7 +1919,7 @@
         <v>-0.1028018435345398</v>
       </c>
       <c r="H35" t="n">
-        <v>37.19</v>
+        <v>50.95</v>
       </c>
       <c r="I35" t="n">
         <v>-34.07262021589793</v>
@@ -1830,6 +1929,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K35" t="n">
+        <v>37.19</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1860,7 +1962,7 @@
         <v>-7.063967310949983</v>
       </c>
       <c r="H36" t="n">
-        <v>47.49</v>
+        <v>47.155</v>
       </c>
       <c r="I36" t="n">
         <v>68.27483829922593</v>
@@ -1870,6 +1972,9 @@
           <t>Caution</t>
         </is>
       </c>
+      <c r="K36" t="n">
+        <v>47.49</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1900,7 +2005,7 @@
         <v>0.06861811283803056</v>
       </c>
       <c r="H37" t="n">
-        <v>53.635</v>
+        <v>47.155</v>
       </c>
       <c r="I37" t="n">
         <v>52.45467076662072</v>
@@ -1910,6 +2015,9 @@
           <t>Caution</t>
         </is>
       </c>
+      <c r="K37" t="n">
+        <v>53.635</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1940,15 +2048,18 @@
         <v>0.01328569587780193</v>
       </c>
       <c r="H38" t="n">
+        <v>47.155</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-3.700561976460615</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>55.345</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-3.700561976460618</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="39">
@@ -1980,7 +2091,7 @@
         <v>3.839131751270119</v>
       </c>
       <c r="H39" t="n">
-        <v>62.05</v>
+        <v>63.63</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -1990,6 +2101,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K39" t="n">
+        <v>62.05</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2020,7 +2134,7 @@
         <v>4.412519521183551</v>
       </c>
       <c r="H40" t="n">
-        <v>31.84</v>
+        <v>34.24</v>
       </c>
       <c r="I40" t="n">
         <v>44.33411214953271</v>
@@ -2030,6 +2144,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K40" t="n">
+        <v>31.84</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2060,7 +2177,7 @@
         <v>-6.151706657367163</v>
       </c>
       <c r="H41" t="n">
-        <v>52.28</v>
+        <v>34.24</v>
       </c>
       <c r="I41" t="n">
         <v>47.75116822429906</v>
@@ -2070,6 +2187,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K41" t="n">
+        <v>52.28</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2079,8 +2199,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero MotoCorp Ltd
-</t>
+          <t>Hero MotoCorp Ltd</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2101,15 +2220,18 @@
         <v>0.1942386275072222</v>
       </c>
       <c r="H42" t="n">
+        <v>38.005</v>
+      </c>
+      <c r="I42" t="n">
+        <v>41.71819497434548</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>60.27500000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>41.71819497434547</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="43">
@@ -2141,15 +2263,18 @@
         <v>1.355289512628809</v>
       </c>
       <c r="H43" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.492268967997123</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
         <v>51.02</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.492268967997133</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="44">
@@ -2160,8 +2285,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindustan Unilever Ltd
-</t>
+          <t>Hindustan Unilever Ltd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2182,7 +2306,7 @@
         <v>1.848273624075064</v>
       </c>
       <c r="H44" t="n">
-        <v>21.805</v>
+        <v>50.95</v>
       </c>
       <c r="I44" t="n">
         <v>-32.26692836113838</v>
@@ -2192,6 +2316,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K44" t="n">
+        <v>21.805</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2222,15 +2349,18 @@
         <v>0.9510909711578005</v>
       </c>
       <c r="H45" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-24.76635514018691</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
         <v>50.57</v>
-      </c>
-      <c r="I45" t="n">
-        <v>-24.76635514018692</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="46">
@@ -2262,15 +2392,18 @@
         <v>0.03821387979852416</v>
       </c>
       <c r="H46" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I46" t="n">
+        <v>43.10747663551402</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>52.4</v>
-      </c>
-      <c r="I46" t="n">
-        <v>43.10747663551401</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="47">
@@ -2302,7 +2435,7 @@
         <v>0.006574879059013327</v>
       </c>
       <c r="H47" t="n">
-        <v>44.31</v>
+        <v>34.24</v>
       </c>
       <c r="I47" t="n">
         <v>-39.16471962616824</v>
@@ -2312,6 +2445,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K47" t="n">
+        <v>44.31</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2342,15 +2478,18 @@
         <v>0.9056027172386589</v>
       </c>
       <c r="H48" t="n">
+        <v>38.005</v>
+      </c>
+      <c r="I48" t="n">
+        <v>100.5788712011578</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>53.7</v>
-      </c>
-      <c r="I48" t="n">
-        <v>100.5788712011577</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
       </c>
     </row>
     <row r="49">
@@ -2382,7 +2521,7 @@
         <v>-0.9664534641259643</v>
       </c>
       <c r="H49" t="n">
-        <v>56</v>
+        <v>34.24</v>
       </c>
       <c r="I49" t="n">
         <v>-73.74415887850468</v>
@@ -2392,6 +2531,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K49" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2422,7 +2564,7 @@
         <v>1.808627454139422</v>
       </c>
       <c r="H50" t="n">
-        <v>34.31</v>
+        <v>63.63</v>
       </c>
       <c r="I50" t="n">
         <v>-43.43862957724344</v>
@@ -2432,6 +2574,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K50" t="n">
+        <v>34.31</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2441,8 +2586,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indian Oil Corporation
-</t>
+          <t>Indian Oil Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2463,7 +2607,7 @@
         <v>2.794810104975634</v>
       </c>
       <c r="H51" t="n">
-        <v>49.11</v>
+        <v>44.915</v>
       </c>
       <c r="I51" t="n">
         <v>-36.30190359568073</v>
@@ -2473,6 +2617,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K51" t="n">
+        <v>49.11</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2503,7 +2650,7 @@
         <v>0.05299874823631171</v>
       </c>
       <c r="H52" t="n">
-        <v>45.585</v>
+        <v>38.005</v>
       </c>
       <c r="I52" t="n">
         <v>59.03170635442703</v>
@@ -2513,6 +2660,9 @@
           <t>Caution</t>
         </is>
       </c>
+      <c r="K52" t="n">
+        <v>45.585</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2543,7 +2693,7 @@
         <v>0.3019460457018293</v>
       </c>
       <c r="H53" t="n">
-        <v>36.52</v>
+        <v>34.24</v>
       </c>
       <c r="I53" t="n">
         <v>-71.34929906542055</v>
@@ -2553,6 +2703,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K53" t="n">
+        <v>36.52</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2562,8 +2715,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITC Ltd
-</t>
+          <t>ITC Ltd</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2584,15 +2736,18 @@
         <v>5.641008076014133</v>
       </c>
       <c r="H54" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-6.08439646712463</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
         <v>62.555</v>
-      </c>
-      <c r="I54" t="n">
-        <v>-6.084396467124634</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="55">
@@ -2624,7 +2779,7 @@
         <v>-0.5890244225007633</v>
       </c>
       <c r="H55" t="n">
-        <v>43.26</v>
+        <v>55.62</v>
       </c>
       <c r="I55" t="n">
         <v>39.59007551240561</v>
@@ -2634,6 +2789,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K55" t="n">
+        <v>43.26</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2664,7 +2822,7 @@
         <v>0.05443098966974722</v>
       </c>
       <c r="H56" t="n">
-        <v>50.11</v>
+        <v>34.24</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -2674,6 +2832,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K56" t="n">
+        <v>50.11</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2704,7 +2865,7 @@
         <v>-1.77053361249378</v>
       </c>
       <c r="H57" t="n">
-        <v>37.545</v>
+        <v>44.915</v>
       </c>
       <c r="I57" t="n">
         <v>-44.80685739730602</v>
@@ -2714,6 +2875,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K57" t="n">
+        <v>37.545</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2744,15 +2908,18 @@
         <v>-0.09143985264473488</v>
       </c>
       <c r="H58" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="I58" t="n">
+        <v>24.54153182308523</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
         <v>35.885</v>
-      </c>
-      <c r="I58" t="n">
-        <v>24.54153182308522</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="59">
@@ -2763,8 +2930,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kotak Mahindra Bank Ltd
-</t>
+          <t>Kotak Mahindra Bank Ltd</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2785,15 +2951,18 @@
         <v>1.572670875827523</v>
       </c>
       <c r="H59" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-3.913551401869164</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>46.535</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-3.913551401869168</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="60">
@@ -2825,15 +2994,18 @@
         <v>0.4646382763782856</v>
       </c>
       <c r="H60" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-10.42640186915887</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
         <v>34.485</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-10.42640186915888</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="61">
@@ -2865,15 +3037,18 @@
         <v>-0.03595279056427525</v>
       </c>
       <c r="H61" t="n">
+        <v>49.105</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5.793707361775779</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
         <v>52.13</v>
-      </c>
-      <c r="I61" t="n">
-        <v>5.793707361775784</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="62">
@@ -2905,15 +3080,18 @@
         <v>1.817983767525715</v>
       </c>
       <c r="H62" t="n">
+        <v>47.155</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-34.68349061605343</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
         <v>24.09</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-34.68349061605344</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
       </c>
     </row>
     <row r="63">
@@ -2945,15 +3123,18 @@
         <v>0.1300622866212008</v>
       </c>
       <c r="H63" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.398711299701394</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
         <v>60.765</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1.398711299701388</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="64">
@@ -2964,8 +3145,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
-</t>
+          <t>Mahindra &amp; Mahindra Ltd</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2986,7 +3166,7 @@
         <v>-0.2694648852484086</v>
       </c>
       <c r="H64" t="n">
-        <v>43.58</v>
+        <v>38.005</v>
       </c>
       <c r="I64" t="n">
         <v>-62.58387054334956</v>
@@ -2996,6 +3176,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K64" t="n">
+        <v>43.58</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3026,7 +3209,7 @@
         <v>0.3282212496887102</v>
       </c>
       <c r="H65" t="n">
-        <v>28.565</v>
+        <v>38.005</v>
       </c>
       <c r="I65" t="n">
         <v>-45.3229838179187</v>
@@ -3036,6 +3219,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K65" t="n">
+        <v>28.565</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3066,7 +3252,7 @@
         <v>0.6329063689949501</v>
       </c>
       <c r="H66" t="n">
-        <v>31.5</v>
+        <v>38.005</v>
       </c>
       <c r="I66" t="n">
         <v>-74.89803973161426</v>
@@ -3076,6 +3262,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K66" t="n">
+        <v>31.5</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3106,7 +3295,7 @@
         <v>-0.02660402589146366</v>
       </c>
       <c r="H67" t="n">
-        <v>34.88500000000001</v>
+        <v>48.33</v>
       </c>
       <c r="I67" t="n">
         <v>-31.96772191185599</v>
@@ -3116,6 +3305,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K67" t="n">
+        <v>34.88500000000001</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3146,15 +3338,18 @@
         <v>0.175112852872738</v>
       </c>
       <c r="H68" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="I68" t="n">
+        <v>7.870461236506365</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
         <v>50.585</v>
-      </c>
-      <c r="I68" t="n">
-        <v>7.870461236506375</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="69">
@@ -3165,8 +3360,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHPC Ltd
-</t>
+          <t>NHPC Ltd</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3187,15 +3381,18 @@
         <v>0.05573417784977254</v>
       </c>
       <c r="H69" t="n">
+        <v>44.915</v>
+      </c>
+      <c r="I69" t="n">
+        <v>58.4548591784482</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
         <v>59.83</v>
-      </c>
-      <c r="I69" t="n">
-        <v>58.45485917844818</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
       </c>
     </row>
     <row r="70">
@@ -3227,7 +3424,7 @@
         <v>0.9521678733206076</v>
       </c>
       <c r="H70" t="n">
-        <v>44.12</v>
+        <v>44.915</v>
       </c>
       <c r="I70" t="n">
         <v>-31.42602693977513</v>
@@ -3237,6 +3434,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K70" t="n">
+        <v>44.12</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3267,7 +3467,7 @@
         <v>10.78154540867274</v>
       </c>
       <c r="H71" t="n">
-        <v>44.31</v>
+        <v>44.915</v>
       </c>
       <c r="I71" t="n">
         <v>-59.59033730379606</v>
@@ -3277,6 +3477,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K71" t="n">
+        <v>44.31</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3307,15 +3510,18 @@
         <v>-5.031547988302576</v>
       </c>
       <c r="H72" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3.971962616822422</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
         <v>35.95</v>
-      </c>
-      <c r="I72" t="n">
-        <v>3.971962616822428</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="73">
@@ -3347,15 +3553,18 @@
         <v>0.588510137595519</v>
       </c>
       <c r="H73" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-35.05933117583603</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
         <v>37.11499999999999</v>
-      </c>
-      <c r="I73" t="n">
-        <v>-35.05933117583604</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
       </c>
     </row>
     <row r="74">
@@ -3387,7 +3596,7 @@
         <v>-1.612606778720886</v>
       </c>
       <c r="H74" t="n">
-        <v>20.58</v>
+        <v>34.24</v>
       </c>
       <c r="I74" t="n">
         <v>-43.6623831775701</v>
@@ -3397,6 +3606,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K74" t="n">
+        <v>20.58</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3427,15 +3639,18 @@
         <v>6.488733930345523</v>
       </c>
       <c r="H75" t="n">
+        <v>44.915</v>
+      </c>
+      <c r="I75" t="n">
+        <v>43.35967939441168</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
         <v>50.86</v>
-      </c>
-      <c r="I75" t="n">
-        <v>43.35967939441167</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="76">
@@ -3467,15 +3682,18 @@
         <v>-20.40097504287343</v>
       </c>
       <c r="H76" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-8.03154205607478</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
         <v>43.34</v>
-      </c>
-      <c r="I76" t="n">
-        <v>-8.031542056074777</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="77">
@@ -3486,8 +3704,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reliance Industries Ltd
-</t>
+          <t>Reliance Industries Ltd</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3508,15 +3725,18 @@
         <v>10.45314512446346</v>
       </c>
       <c r="H77" t="n">
+        <v>44.915</v>
+      </c>
+      <c r="I77" t="n">
+        <v>29.88979182901037</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
         <v>50.5</v>
-      </c>
-      <c r="I77" t="n">
-        <v>29.88979182901036</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="78">
@@ -3548,7 +3768,7 @@
         <v>-0.2368813254240325</v>
       </c>
       <c r="H78" t="n">
-        <v>54.025</v>
+        <v>34.24</v>
       </c>
       <c r="I78" t="n">
         <v>104.3808411214953</v>
@@ -3558,6 +3778,9 @@
           <t>Caution</t>
         </is>
       </c>
+      <c r="K78" t="n">
+        <v>54.025</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3588,7 +3811,7 @@
         <v>0.7563625783740417</v>
       </c>
       <c r="H79" t="n">
-        <v>50.985</v>
+        <v>34.24</v>
       </c>
       <c r="I79" t="n">
         <v>60.42640186915887</v>
@@ -3598,6 +3821,9 @@
           <t>Caution</t>
         </is>
       </c>
+      <c r="K79" t="n">
+        <v>50.985</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3628,15 +3854,18 @@
         <v>0.06115348347250073</v>
       </c>
       <c r="H80" t="n">
+        <v>55.62</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-53.48795397339086</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
         <v>33.97</v>
-      </c>
-      <c r="I80" t="n">
-        <v>-53.48795397339087</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
       </c>
     </row>
     <row r="81">
@@ -3647,8 +3876,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shriram Finance Ltd
-</t>
+          <t>Shriram Finance Ltd</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3669,15 +3897,18 @@
         <v>-3.608906905151208</v>
       </c>
       <c r="H81" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I81" t="n">
+        <v>100.1460280373831</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
         <v>47.26000000000001</v>
-      </c>
-      <c r="I81" t="n">
-        <v>100.1460280373832</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
       </c>
     </row>
     <row r="82">
@@ -3709,15 +3940,18 @@
         <v>0.09804152402695152</v>
       </c>
       <c r="H82" t="n">
+        <v>47.155</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-29.33941257554873</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
         <v>37.225</v>
-      </c>
-      <c r="I82" t="n">
-        <v>-29.33941257554872</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="83">
@@ -3749,7 +3983,7 @@
         <v>0.8489189373413096</v>
       </c>
       <c r="H83" t="n">
-        <v>31.24</v>
+        <v>47.06</v>
       </c>
       <c r="I83" t="n">
         <v>-19.46451338716533</v>
@@ -3759,6 +3993,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K83" t="n">
+        <v>31.24</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3789,15 +4026,18 @@
         <v>0.007417056977403794</v>
       </c>
       <c r="H84" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="I84" t="n">
+        <v>7.536800785083408</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
         <v>37.655</v>
-      </c>
-      <c r="I84" t="n">
-        <v>7.536800785083407</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="85">
@@ -3829,7 +4069,7 @@
         <v>3.000651602734764</v>
       </c>
       <c r="H85" t="n">
-        <v>31.715</v>
+        <v>38.005</v>
       </c>
       <c r="I85" t="n">
         <v>76.47677937113535</v>
@@ -3839,6 +4079,9 @@
           <t>Caution</t>
         </is>
       </c>
+      <c r="K85" t="n">
+        <v>31.715</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3848,8 +4091,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tata Power Company Ltd
-</t>
+          <t>Tata Power Company Ltd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3870,7 +4112,7 @@
         <v>0.2166615750083587</v>
       </c>
       <c r="H86" t="n">
-        <v>23.51</v>
+        <v>44.915</v>
       </c>
       <c r="I86" t="n">
         <v>-67.71679839697205</v>
@@ -3880,6 +4122,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K86" t="n">
+        <v>23.51</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3889,8 +4134,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tata Steel Ltd
-</t>
+          <t>Tata Steel Ltd</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3911,7 +4155,7 @@
         <v>1.638533052351645</v>
       </c>
       <c r="H87" t="n">
-        <v>50.555</v>
+        <v>55.62</v>
       </c>
       <c r="I87" t="n">
         <v>-11.95613088816972</v>
@@ -3921,6 +4165,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K87" t="n">
+        <v>50.555</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3951,7 +4198,7 @@
         <v>10.93458277277939</v>
       </c>
       <c r="H88" t="n">
-        <v>52.365</v>
+        <v>63.63</v>
       </c>
       <c r="I88" t="n">
         <v>23.66808109382366</v>
@@ -3961,6 +4208,9 @@
           <t>Fair</t>
         </is>
       </c>
+      <c r="K88" t="n">
+        <v>52.365</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3991,15 +4241,18 @@
         <v>0.1674227036387368</v>
       </c>
       <c r="H89" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-9.790979097909801</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
         <v>49.445</v>
-      </c>
-      <c r="I89" t="n">
-        <v>-9.790979097909796</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="90">
@@ -4010,8 +4263,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Titan Company Ltd
-</t>
+          <t>Titan Company Ltd</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4032,15 +4284,18 @@
         <v>0.0839572651499547</v>
       </c>
       <c r="H90" t="n">
+        <v>38.005</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-73.3456124194185</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Discount</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
         <v>27.58</v>
-      </c>
-      <c r="I90" t="n">
-        <v>-73.34561241941849</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Discount</t>
-        </is>
       </c>
     </row>
     <row r="91">
@@ -4072,15 +4327,18 @@
         <v>0.1660811237632738</v>
       </c>
       <c r="H91" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-1.402464938376546</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
         <v>48.83</v>
-      </c>
-      <c r="I91" t="n">
-        <v>-1.402464938376548</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
     <row r="92">
@@ -4112,7 +4370,7 @@
         <v>0.1472024429514394</v>
       </c>
       <c r="H92" t="n">
-        <v>67.02</v>
+        <v>38.005</v>
       </c>
       <c r="I92" t="n">
         <v>-77.23983686357059</v>
@@ -4122,6 +4380,9 @@
           <t>Discount</t>
         </is>
       </c>
+      <c r="K92" t="n">
+        <v>67.02</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4152,15 +4413,18 @@
         <v>-0.8454886074536311</v>
       </c>
       <c r="H93" t="n">
+        <v>38.005</v>
+      </c>
+      <c r="I93" t="n">
+        <v>21.29982896987237</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
         <v>35.19</v>
-      </c>
-      <c r="I93" t="n">
-        <v>21.29982896987238</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
       </c>
     </row>
   </sheetData>
